--- a/feedback_forms/007_gym_trainer_certification_feedback_survey--feedback_forms.xlsx
+++ b/feedback_forms/007_gym_trainer_certification_feedback_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'increase'}</t>
+          <t>increase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Increase'}</t>
+          <t>Increase</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'improve'}</t>
+          <t>improve</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Improve'}</t>
+          <t>Improve</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'no_action'}</t>
+          <t>no_action</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'No Action'}</t>
+          <t>No Action</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'do_not_submit'}</t>
+          <t>do_not_submit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Do Not Submit'}</t>
+          <t>Do Not Submit</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'save_for_later'}</t>
+          <t>save_for_later</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Save For Later'}</t>
+          <t>Save For Later</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'certified'}</t>
+          <t>certified</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Certified'}</t>
+          <t>Certified</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'non-certified'}</t>
+          <t>non-certified</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Non-Certified'}</t>
+          <t>Non-Certified</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'group_class'}</t>
+          <t>group_class</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Group Class'}</t>
+          <t>Group Class</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'one-on-one'}</t>
+          <t>one-on-one</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'One-On-One'}</t>
+          <t>One-On-One</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
